--- a/auto_gen_package/data_output/output-目标端监控ips.xlsx
+++ b/auto_gen_package/data_output/output-目标端监控ips.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>003069</t>
+          <t>014936</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>陈雪姣</t>
+          <t>胡昊辰</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.187.20.21</t>
+          <t>10.187.108.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,17 +468,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>003071</t>
+          <t>003240</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>杨莉</t>
+          <t>金晶</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.187.20.22</t>
+          <t>10.187.108.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,17 +490,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>003340</t>
+          <t>010776</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>黄艺</t>
+          <t>邱俊华</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.187.20.24</t>
+          <t>10.187.108.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,17 +512,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>003342</t>
+          <t>013978</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>徐泠璐</t>
+          <t>胡淑雅</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10.187.20.25</t>
+          <t>10.187.108.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>003351</t>
+          <t>002506</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>曹贞贞</t>
+          <t>施徐红</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10.187.20.26</t>
+          <t>10.187.108.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>003724</t>
+          <t>023145</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周妍</t>
+          <t>王天翊</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10.187.20.27</t>
+          <t>10.187.108.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,17 +578,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>003726</t>
+          <t>017337</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>冷眉</t>
+          <t>杭一苇</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10.187.20.28</t>
+          <t>10.187.108.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,17 +600,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>003727</t>
+          <t>013525</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>庞科佳</t>
+          <t>王栩淳</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10.187.20.29</t>
+          <t>10.187.108.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,17 +622,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>003729</t>
+          <t>006694</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>郭丽丽</t>
+          <t>韩澄忱</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10.187.20.30</t>
+          <t>10.187.108.29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,17 +644,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>003733</t>
+          <t>003728</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>黄苏丹</t>
+          <t>孙博</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10.187.20.31</t>
+          <t>10.187.108.30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>004041</t>
+          <t>002260</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>于漪云</t>
+          <t>丁悦悦</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10.187.20.32</t>
+          <t>10.187.108.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,17 +688,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>004656</t>
+          <t>001874</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>朱宏艳</t>
+          <t>黄叶轩</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10.187.20.34</t>
+          <t>10.187.108.32</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,17 +710,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>004660</t>
+          <t>001709</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>孟娜</t>
+          <t>刘娟娟</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10.187.20.35</t>
+          <t>10.187.108.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,17 +732,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>004761</t>
+          <t>003316</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>高静</t>
+          <t>钱佳</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10.187.20.36</t>
+          <t>10.187.108.34</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,17 +754,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>004763</t>
+          <t>011533</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>韩月蓓</t>
+          <t>卢山</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10.187.20.37</t>
+          <t>10.187.108.35</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,17 +776,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>004778</t>
+          <t>004974</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>施进进</t>
+          <t>唐静曌</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10.187.20.39</t>
+          <t>10.187.108.36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -798,17 +798,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>004783</t>
+          <t>004653</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>吴健</t>
+          <t>闫方露</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10.187.20.40</t>
+          <t>10.187.108.37</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -820,17 +820,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>004784</t>
+          <t>002494</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>夏宇斌</t>
+          <t>朱有为</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10.187.20.41</t>
+          <t>10.187.108.38</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,17 +842,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>004793</t>
+          <t>002257</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>刘宏</t>
+          <t>徐燕</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10.187.20.42</t>
+          <t>10.187.108.39</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,17 +864,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>004800</t>
+          <t>002155</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>王瑶</t>
+          <t>张徐健</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10.187.20.43</t>
+          <t>10.187.108.40</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -886,17 +886,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>004810</t>
+          <t>024785</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>石久霞</t>
+          <t>孙丽颖</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10.187.20.44</t>
+          <t>10.187.108.41</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,17 +908,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>004829</t>
+          <t>021865</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>赵美</t>
+          <t>张又心</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10.187.20.45</t>
+          <t>10.187.108.42</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -930,17 +930,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>004831</t>
+          <t>026030</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>林琳</t>
+          <t>王千一</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10.187.20.46</t>
+          <t>10.187.108.43</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,17 +952,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>004838</t>
+          <t>015574</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>冯炜炜</t>
+          <t>霍耀璞</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10.187.20.47</t>
+          <t>10.187.108.44</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -974,17 +974,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>004944</t>
+          <t>017014</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>罗国帼</t>
+          <t>房夏莲</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.187.20.48</t>
+          <t>10.187.108.45</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -996,17 +996,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>004945</t>
+          <t>020253</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>徐敏</t>
+          <t>陈熹熹</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10.187.20.49</t>
+          <t>10.187.108.46</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,17 +1018,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>004976</t>
+          <t>011697</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>季冰倩</t>
+          <t>许世豪</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10.187.20.50</t>
+          <t>10.187.108.47</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,17 +1040,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>005932</t>
+          <t>010301</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>陈颖</t>
+          <t>胡金有</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10.187.20.52</t>
+          <t>10.187.108.48</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,105 +1062,105 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>005933</t>
+          <t>006006</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>李静</t>
+          <t>江峰</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10.187.20.53</t>
+          <t>10.187.108.49</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10.191.240.12</t>
+          <t>10.191.240.11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>024751</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>陈云云</t>
+          <t>陈龙</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10.187.20.54</t>
+          <t>10.187.108.50</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10.191.240.12</t>
+          <t>10.191.240.11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>005965</t>
+          <t>024342</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>王娟</t>
+          <t>解波</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10.187.20.56</t>
+          <t>10.187.108.51</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10.191.240.10</t>
+          <t>10.191.240.11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>005966</t>
+          <t>023976</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>魏卉</t>
+          <t>张贵军</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10.187.20.57</t>
+          <t>10.187.108.52</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10.191.240.12</t>
+          <t>10.191.240.11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>005967</t>
+          <t>018018</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>朱静波</t>
+          <t>史思旗</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10.187.20.58</t>
+          <t>10.187.92.21</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1172,17 +1172,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>005971</t>
+          <t>002185</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>薛文玉</t>
+          <t>申琳</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10.187.20.59</t>
+          <t>10.187.92.22</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1194,17 +1194,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>006815</t>
+          <t>023112</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>张思凡</t>
+          <t>李智</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10.187.20.60</t>
+          <t>10.187.92.23</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1216,17 +1216,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>006818</t>
+          <t>015586</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>刘星雨</t>
+          <t>任皓麟</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10.187.20.61</t>
+          <t>10.187.92.24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1238,17 +1238,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>006819</t>
+          <t>014251</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>曹贵萍</t>
+          <t>杨立群</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10.187.20.62</t>
+          <t>10.187.92.25</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1260,17 +1260,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>006823</t>
+          <t>018208</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>陈白杨</t>
+          <t>王刚</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10.187.20.63</t>
+          <t>10.187.92.26</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1282,17 +1282,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>006826</t>
+          <t>016875</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>李琪</t>
+          <t>龚志远</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10.187.20.64</t>
+          <t>10.187.92.27</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1304,17 +1304,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>006880</t>
+          <t>010521</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>王若琪</t>
+          <t>朱凌峰</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10.187.20.65</t>
+          <t>10.187.92.28</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1326,17 +1326,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>006965</t>
+          <t>017771</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>王玲</t>
+          <t>胡颖</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10.187.20.66</t>
+          <t>10.187.92.29</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1348,17 +1348,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>006966</t>
+          <t>010796</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>施秋艳</t>
+          <t>张朕</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10.187.20.67</t>
+          <t>10.187.92.30</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1370,105 +1370,105 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>006967</t>
+          <t>014334</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>王倩倩</t>
+          <t>胡亚霜</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10.187.20.68</t>
+          <t>10.187.92.31</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.191.240.13</t>
+          <t>10.191.240.12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>010226</t>
+          <t>010801</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>焦丹</t>
+          <t>訾立杰</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10.187.20.69</t>
+          <t>10.187.92.32</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.191.240.13</t>
+          <t>10.191.240.12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>010229</t>
+          <t>016451</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>鲍婷</t>
+          <t>吕文靖</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10.187.20.70</t>
+          <t>10.187.92.33</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10.191.240.13</t>
+          <t>10.191.240.12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>010230</t>
+          <t>015545</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>蔡燕</t>
+          <t>孙维婷</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10.187.20.71</t>
+          <t>10.187.92.34</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.191.240.13</t>
+          <t>10.191.240.12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>010233</t>
+          <t>020254</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>贾淼杰</t>
+          <t>张衡</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>10.187.20.72</t>
+          <t>10.187.92.35</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1480,17 +1480,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>010234</t>
+          <t>002151</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>王莹</t>
+          <t>叶青青</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10.187.20.73</t>
+          <t>10.187.92.36</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1502,17 +1502,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>010239</t>
+          <t>010741</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>汪蕾</t>
+          <t>韩笑</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10.187.20.74</t>
+          <t>10.187.92.37</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1524,17 +1524,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>010275</t>
+          <t>006689</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>朱文君</t>
+          <t>程志远</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10.187.20.76</t>
+          <t>10.187.92.38</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1546,17 +1546,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>010286</t>
+          <t>018455</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>吕品</t>
+          <t>张志鼎</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>10.187.20.78</t>
+          <t>10.187.92.39</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1568,17 +1568,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>010317</t>
+          <t>012192</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>孙楚楚</t>
+          <t>陈隽尧</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10.187.20.79</t>
+          <t>10.187.92.40</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1590,17 +1590,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>010552</t>
+          <t>011466</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>钱锐</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10.187.20.80</t>
+          <t>10.187.92.41</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1612,17 +1612,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>010905</t>
+          <t>011658</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>江天琦</t>
+          <t>刘照</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10.187.20.82</t>
+          <t>10.187.92.42</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1634,17 +1634,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>010908</t>
+          <t>020336</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>邱子菡</t>
+          <t>余昃阳</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10.187.20.83</t>
+          <t>10.187.92.43</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1656,17 +1656,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>010909</t>
+          <t>014345</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>何松青</t>
+          <t>刘永</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10.187.20.84</t>
+          <t>10.187.92.44</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1678,303 +1678,303 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>010914</t>
+          <t>013006</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>焦丽琴</t>
+          <t>吴达</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10.187.20.85</t>
+          <t>10.187.92.45</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>010916</t>
+          <t>016187</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>潘聪芳</t>
+          <t>王玉涛</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>10.187.20.86</t>
+          <t>10.187.92.46</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>010917</t>
+          <t>001923</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>宫玉蓉</t>
+          <t>单锋</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>10.187.20.87</t>
+          <t>10.187.92.47</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>010918</t>
+          <t>017582</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>张辉</t>
+          <t>顾皓</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>10.187.20.88</t>
+          <t>10.187.92.48</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>010919</t>
+          <t>012797</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>王晓红</t>
+          <t>黄菁</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>10.187.20.89</t>
+          <t>10.187.92.49</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>010941</t>
+          <t>021999</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>陈楠</t>
+          <t>刘畅</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10.187.20.91</t>
+          <t>10.187.92.50</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>010949</t>
+          <t>019419</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>郭丽雅</t>
+          <t>余嘉</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>10.187.20.95</t>
+          <t>10.187.92.51</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>010957</t>
+          <t>022801</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>田雨蓓</t>
+          <t>吕乐雅</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>10.187.20.96</t>
+          <t>10.187.92.52</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>010960</t>
+          <t>005922</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>李怡琴</t>
+          <t>吕建华</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>10.187.20.97</t>
+          <t>10.187.92.53</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>010978</t>
+          <t>016011</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>黄宸婕</t>
+          <t>杨友斌</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10.187.20.99</t>
+          <t>10.187.92.54</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>010979</t>
+          <t>022310</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>陈泽娅</t>
+          <t>全雨庭</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10.187.20.100</t>
+          <t>10.187.92.55</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>011213</t>
+          <t>021896</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>赵月</t>
+          <t>吴凡灿</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>10.187.20.101</t>
+          <t>10.187.92.56</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>011215</t>
+          <t>016531</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>唐瑜</t>
+          <t>杨友林</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>10.187.20.102</t>
+          <t>10.187.92.57</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10.191.240.14</t>
+          <t>10.191.240.13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>011217</t>
+          <t>005931</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>项洋</t>
+          <t>翁琪惠</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>10.187.20.103</t>
+          <t>10.187.92.58</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1986,1076 +1986,1968 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>011219</t>
+          <t>011170</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>安莉</t>
+          <t>管艺文</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10.187.20.105</t>
+          <t>10.187.92.59</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>011223</t>
+          <t>004615</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>吴琼</t>
+          <t>胡晟</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10.187.20.106</t>
+          <t>10.187.92.60</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>011225</t>
+          <t>016837</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>霍小六</t>
+          <t>陈将</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10.187.20.107</t>
+          <t>10.187.92.62</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>011232</t>
+          <t>016185</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>陶悦</t>
+          <t>王铁勋</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10.187.20.108</t>
+          <t>10.187.92.63</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>011234</t>
+          <t>013518</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>刘佳</t>
+          <t>李蕾</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10.187.20.110</t>
+          <t>10.187.92.64</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>011236</t>
+          <t>006072</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>贾明惠</t>
+          <t>贾志军</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10.187.20.111</t>
+          <t>10.187.92.65</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>011590</t>
+          <t>006027</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>余磊</t>
+          <t>杨洁</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10.187.20.113</t>
+          <t>10.187.92.66</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>011594</t>
+          <t>004647</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>冯晨</t>
+          <t>高颖</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10.187.20.115</t>
+          <t>10.187.92.67</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>011803</t>
+          <t>004628</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>强薇</t>
+          <t>肖奇</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10.187.20.116</t>
+          <t>10.187.92.68</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>011804</t>
+          <t>004026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>李琳</t>
+          <t>刘也琪</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10.187.20.117</t>
+          <t>10.187.92.69</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>011805</t>
+          <t>002436</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>顾亚洁</t>
+          <t>闵煌</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10.187.20.118</t>
+          <t>10.187.92.70</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>011831</t>
+          <t>002371</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>纪哲康</t>
+          <t>吴培生</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>10.187.20.119</t>
+          <t>10.187.92.71</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>011835</t>
+          <t>001260</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>姚润东</t>
+          <t>张英黎</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10.187.20.121</t>
+          <t>10.187.92.72</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>011838</t>
+          <t>011660</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>朱豆豆</t>
+          <t>苗家伟</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10.187.20.123</t>
+          <t>10.187.92.73</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10.191.240.15</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>011839</t>
+          <t>011659</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>张钰晨</t>
+          <t>马元</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10.187.20.124</t>
+          <t>10.187.92.74</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>011841</t>
+          <t>016441</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>冀青峰</t>
+          <t>张瑞斌</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10.187.20.125</t>
+          <t>10.187.92.75</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>011842</t>
+          <t>013514</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>乔丽云</t>
+          <t>周文威</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>10.187.20.126</t>
+          <t>10.187.92.76</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>011843</t>
+          <t>012736</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>张杰</t>
+          <t>陈慧</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10.187.20.127</t>
+          <t>10.187.92.77</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>011845</t>
+          <t>010535</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>吴彩梅</t>
+          <t>施元庆</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10.187.20.128</t>
+          <t>10.187.92.78</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>011846</t>
+          <t>024889</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>张晓彤</t>
+          <t>古家乐</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>10.187.20.129</t>
+          <t>10.187.92.79</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>011848</t>
+          <t>024885</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>徐文甜</t>
+          <t>王婉伊</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>10.187.20.130</t>
+          <t>10.187.92.80</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>011850</t>
+          <t>024395</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>朱红梅</t>
+          <t>顾仲谋</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>10.187.20.131</t>
+          <t>10.187.92.81</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>011986</t>
+          <t>023978</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>武丹阳</t>
+          <t>姜妍</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10.187.20.132</t>
+          <t>10.187.92.82</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.14</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>011987</t>
+          <t>022457</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>瞿一凡</t>
+          <t>朱琳</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10.187.20.133</t>
+          <t>10.187.132.21</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>012293</t>
+          <t>017854</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>李洁</t>
+          <t>高瑞</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>10.187.20.136</t>
+          <t>10.187.132.22</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>012415</t>
+          <t>002704</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>叶青</t>
+          <t>范莹</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>10.187.20.139</t>
+          <t>10.187.132.23</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>012464</t>
+          <t>018661</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>程兰岚</t>
+          <t>高娜</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10.187.20.140</t>
+          <t>10.187.132.24</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>012465</t>
+          <t>019199</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>张家琪</t>
+          <t>潘艳梅</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10.187.20.141</t>
+          <t>10.187.132.25</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10.191.240.16</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>012553</t>
+          <t>013718</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>孟思岐</t>
+          <t>柏钰</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>10.187.20.142</t>
+          <t>10.187.132.27</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>012558</t>
+          <t>003555</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>查亚娟</t>
+          <t>王蕾</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>10.187.20.143</t>
+          <t>10.187.132.28</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>012560</t>
+          <t>017496</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>黄诚</t>
+          <t>薛阳</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>10.187.20.144</t>
+          <t>10.187.132.29</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>012561</t>
+          <t>018985</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>王雪辰</t>
+          <t>钱瓖蕙</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>10.187.20.145</t>
+          <t>10.187.132.31</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>012562</t>
+          <t>002746</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>王雨娇</t>
+          <t>马仁敏</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>10.187.20.146</t>
+          <t>10.187.132.32</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>012565</t>
+          <t>016720</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>邓书霖云</t>
+          <t>高雅</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>10.187.20.148</t>
+          <t>10.187.132.33</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>012761</t>
+          <t>004917</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>陈爱娜</t>
+          <t>李玉标</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>10.187.20.150</t>
+          <t>10.187.132.34</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>012857</t>
+          <t>016232</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>时华欣</t>
+          <t>邹颖</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>10.187.20.151</t>
+          <t>10.187.132.36</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>012946</t>
+          <t>011112</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>徐艳红</t>
+          <t>张怡婷</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>10.187.20.154</t>
+          <t>10.187.132.37</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10.191.240.10</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>013110</t>
+          <t>016262</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>焦韵</t>
+          <t>付晟</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>10.187.20.155</t>
+          <t>10.187.132.38</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>013112</t>
+          <t>019963</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>张辰</t>
+          <t>袁晨程</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>10.187.20.156</t>
+          <t>10.187.132.39</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>013114</t>
+          <t>011024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>马佳</t>
+          <t>赵迎</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>10.187.20.157</t>
+          <t>10.187.132.40</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>013436</t>
+          <t>020958</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>李燕霏儿</t>
+          <t>张秦川</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>10.187.20.158</t>
+          <t>10.187.132.41</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>013444</t>
+          <t>020628</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>董思群</t>
+          <t>张明</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>10.187.20.159</t>
+          <t>10.187.132.42</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>013627</t>
+          <t>020401</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>王思佳</t>
+          <t>郑滋煜</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>10.187.20.161</t>
+          <t>10.187.132.43</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>013628</t>
+          <t>016394</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>邵巧</t>
+          <t>郑雨曦</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>10.187.20.162</t>
+          <t>10.187.132.44</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>10.191.240.17</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>021292</t>
+          <t>017623</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>朱思颖</t>
+          <t>崔亮</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>10.187.20.226</t>
+          <t>10.187.132.45</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>10.191.240.11</t>
+          <t>10.191.240.15</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>022521</t>
+          <t>019369</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>高烁然</t>
+          <t>殷晨昊</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>10.187.20.251</t>
+          <t>10.187.132.46</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>10.191.240.12</t>
+          <t>10.191.240.16</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>zyvdidt01</t>
+          <t>016984</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>zyvdidt01</t>
+          <t>孙正楠</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>10.187.21.21</t>
+          <t>10.187.132.47</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>10.191.240.10</t>
+          <t>10.191.240.16</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>zyvdidt02</t>
+          <t>011501</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>zyvdidt02</t>
+          <t>陆殷华</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>10.187.21.22</t>
+          <t>10.187.132.48</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10.191.240.10</t>
+          <t>10.191.240.16</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>011462</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>邱莹莹</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>10.187.132.49</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>009357</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>张琛</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10.187.132.50</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>009159</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>沈晓磊</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>10.187.132.51</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>009157</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>李丹</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10.187.132.52</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>002739</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>陈嘉</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>10.187.132.53</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>002680</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>殷晓磊</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>10.187.132.54</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>002043</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>贾红刚</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>10.187.132.55</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>001901</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>陶军</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>10.187.132.56</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>011264</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>陈凯</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>10.187.132.58</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>011137</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>刘云龙</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>10.187.132.59</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>009242</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>赵耿龙</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>10.187.132.60</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>011461</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>方略</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>10.187.132.61</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>017442</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>李晓童</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>10.187.132.62</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>016845</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>谢凌风</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>10.187.132.63</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>016546</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>蔡祎辰</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>10.187.132.64</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>015110</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>袁建</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>10.187.132.65</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>024451</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>田子春</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>10.187.132.66</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>10.191.240.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>003890</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>康鹏宇</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>10.187.100.21</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>015329</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>陈欢</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>10.187.100.22</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>012252</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>刘子煜</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>10.187.100.23</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>011078</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>王刚</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>10.187.100.24</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>013033</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>陈艳</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>10.187.100.25</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>026267</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>李云蔚</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>10.187.100.26</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>005961</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>马磊</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>10.187.100.27</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>017049</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>俞瑞</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>10.187.100.28</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>002033</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>王华</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>10.187.100.29</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>025565</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>张志宇</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>10.187.100.30</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>001742</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>张鸿兴</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>10.187.100.31</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>014322</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>周元状</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>10.187.100.32</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>025397</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>李童</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>10.187.100.33</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>010637</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>侯永华</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>10.187.100.34</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>001904</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>包晓明</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>10.187.100.35</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>014104</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>姚章龙</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>10.187.100.36</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>017050</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>李喆琦</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>10.187.100.37</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>015584</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>秦娜娜</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>10.187.100.38</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>019491</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>王路遥</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>10.187.100.39</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>006620</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>杨培</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>10.187.100.40</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>010788</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>王玉祥</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>10.187.100.41</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>010812</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>王利学</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>10.187.100.42</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>006247</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>张廷文</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>10.187.100.43</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>10.191.240.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>zyvdidt02</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>zyvdidt02</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>10.191.240.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>zyvdidt03</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>zyvdidt03</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>10.187.21.23</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>10.191.240.10</t>
         </is>
